--- a/booklets/User Stories Mapping.xlsx
+++ b/booklets/User Stories Mapping.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="User Stories to Spreadsheet Map" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'User Stories to Spreadsheet Map'!$A$1:$F$21</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'User Stories to Spreadsheet Map'!$A$1:$F$22</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
   <si>
     <t>ID</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t>Dashboard UI (Rule Manager Toggle)</t>
+  </si>
+  <si>
+    <t>US21</t>
+  </si>
+  <si>
+    <t>Dashboard UI (Triggers &amp; Warnings Tab)</t>
   </si>
 </sst>
 </file>
@@ -414,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F21" displayName="User_Stories" name="User_Stories" id="1">
-  <autoFilter ref="$A$1:$F$21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F22" displayName="User_Stories" name="User_Stories" id="1">
+  <autoFilter ref="$A$1:$F$22"/>
   <tableColumns count="6">
     <tableColumn name="ID" id="1"/>
     <tableColumn name="Role" id="2"/>
@@ -1056,9 +1062,29 @@
         <v>90</v>
       </c>
     </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B21">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B22">
       <formula1>"Botanist,Safety Manager,Energy Engineer,Administrator"</formula1>
     </dataValidation>
   </dataValidations>
